--- a/Outcome/Appendix/figure_data/fig11.xlsx
+++ b/Outcome/Appendix/figure_data/fig11.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -226,15 +226,6 @@
   <si>
     <t xml:space="preserve">Liver fluke</t>
   </si>
-  <si>
-    <t xml:space="preserve">Paratyphoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cholera</t>
-  </si>
 </sst>
 </file>
 
@@ -289,8 +280,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M433" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M433"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M337" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M337"/>
   <tableColumns count="13">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="mean"/>
@@ -14409,3942 +14400,6 @@
         <v>64</v>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="B338" t="n">
-        <v>19.7741853093301</v>
-      </c>
-      <c r="C338" t="n">
-        <v>12.804588500894</v>
-      </c>
-      <c r="D338" t="n">
-        <v>9.09286094687733</v>
-      </c>
-      <c r="E338" t="n">
-        <v>30.4468740530476</v>
-      </c>
-      <c r="F338" t="n">
-        <v>36.5262060176456</v>
-      </c>
-      <c r="G338" t="s">
-        <v>71</v>
-      </c>
-      <c r="H338" t="n">
-        <v>14</v>
-      </c>
-      <c r="I338" t="n">
-        <v>6</v>
-      </c>
-      <c r="J338" t="s">
-        <v>21</v>
-      </c>
-      <c r="K338" t="n">
-        <v>1.412</v>
-      </c>
-      <c r="L338" t="s">
-        <v>15</v>
-      </c>
-      <c r="M338" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="1" t="n">
-        <v>43862</v>
-      </c>
-      <c r="B339" t="n">
-        <v>18.1540827763162</v>
-      </c>
-      <c r="C339" t="n">
-        <v>11.0009010657204</v>
-      </c>
-      <c r="D339" t="n">
-        <v>8.83297661683107</v>
-      </c>
-      <c r="E339" t="n">
-        <v>28.1363586906688</v>
-      </c>
-      <c r="F339" t="n">
-        <v>35.9209806992572</v>
-      </c>
-      <c r="G339" t="s">
-        <v>71</v>
-      </c>
-      <c r="H339" t="n">
-        <v>14</v>
-      </c>
-      <c r="I339" t="n">
-        <v>4</v>
-      </c>
-      <c r="J339" t="s">
-        <v>21</v>
-      </c>
-      <c r="K339" t="n">
-        <v>1.297</v>
-      </c>
-      <c r="L339" t="s">
-        <v>15</v>
-      </c>
-      <c r="M339" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="B340" t="n">
-        <v>15.8829538337555</v>
-      </c>
-      <c r="C340" t="n">
-        <v>9.50755700659331</v>
-      </c>
-      <c r="D340" t="n">
-        <v>7.30178436987279</v>
-      </c>
-      <c r="E340" t="n">
-        <v>26.8941059383323</v>
-      </c>
-      <c r="F340" t="n">
-        <v>33.7497035661165</v>
-      </c>
-      <c r="G340" t="s">
-        <v>71</v>
-      </c>
-      <c r="H340" t="n">
-        <v>4</v>
-      </c>
-      <c r="I340" t="n">
-        <v>12</v>
-      </c>
-      <c r="J340" t="s">
-        <v>21</v>
-      </c>
-      <c r="K340" t="n">
-        <v>3.963</v>
-      </c>
-      <c r="L340" t="s">
-        <v>15</v>
-      </c>
-      <c r="M340" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="1" t="n">
-        <v>43922</v>
-      </c>
-      <c r="B341" t="n">
-        <v>14.9269498889898</v>
-      </c>
-      <c r="C341" t="n">
-        <v>8.48341556900294</v>
-      </c>
-      <c r="D341" t="n">
-        <v>6.35741129048259</v>
-      </c>
-      <c r="E341" t="n">
-        <v>24.8164095769785</v>
-      </c>
-      <c r="F341" t="n">
-        <v>34.0000474318233</v>
-      </c>
-      <c r="G341" t="s">
-        <v>71</v>
-      </c>
-      <c r="H341" t="n">
-        <v>9</v>
-      </c>
-      <c r="I341" t="n">
-        <v>6</v>
-      </c>
-      <c r="J341" t="s">
-        <v>21</v>
-      </c>
-      <c r="K341" t="n">
-        <v>1.658</v>
-      </c>
-      <c r="L341" t="s">
-        <v>15</v>
-      </c>
-      <c r="M341" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="B342" t="n">
-        <v>15.7755030293623</v>
-      </c>
-      <c r="C342" t="n">
-        <v>9.13867076678022</v>
-      </c>
-      <c r="D342" t="n">
-        <v>6.4823932741246</v>
-      </c>
-      <c r="E342" t="n">
-        <v>27.0319532375667</v>
-      </c>
-      <c r="F342" t="n">
-        <v>37.1218329396585</v>
-      </c>
-      <c r="G342" t="s">
-        <v>71</v>
-      </c>
-      <c r="H342" t="n">
-        <v>8</v>
-      </c>
-      <c r="I342" t="n">
-        <v>8</v>
-      </c>
-      <c r="J342" t="s">
-        <v>21</v>
-      </c>
-      <c r="K342" t="n">
-        <v>1.971</v>
-      </c>
-      <c r="L342" t="s">
-        <v>15</v>
-      </c>
-      <c r="M342" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="1" t="n">
-        <v>43983</v>
-      </c>
-      <c r="B343" t="n">
-        <v>24.7041405309</v>
-      </c>
-      <c r="C343" t="n">
-        <v>13.8634065632252</v>
-      </c>
-      <c r="D343" t="n">
-        <v>9.29133230836815</v>
-      </c>
-      <c r="E343" t="n">
-        <v>44.2051391304395</v>
-      </c>
-      <c r="F343" t="n">
-        <v>56.6920534548844</v>
-      </c>
-      <c r="G343" t="s">
-        <v>71</v>
-      </c>
-      <c r="H343" t="n">
-        <v>7</v>
-      </c>
-      <c r="I343" t="n">
-        <v>18</v>
-      </c>
-      <c r="J343" t="s">
-        <v>21</v>
-      </c>
-      <c r="K343" t="n">
-        <v>3.526</v>
-      </c>
-      <c r="L343" t="s">
-        <v>15</v>
-      </c>
-      <c r="M343" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="1" t="n">
-        <v>44013</v>
-      </c>
-      <c r="B344" t="n">
-        <v>18.8616013041033</v>
-      </c>
-      <c r="C344" t="n">
-        <v>10.3359954386863</v>
-      </c>
-      <c r="D344" t="n">
-        <v>6.82552797133228</v>
-      </c>
-      <c r="E344" t="n">
-        <v>34.2008491363473</v>
-      </c>
-      <c r="F344" t="n">
-        <v>43.6632337187222</v>
-      </c>
-      <c r="G344" t="s">
-        <v>71</v>
-      </c>
-      <c r="H344" t="n">
-        <v>11</v>
-      </c>
-      <c r="I344" t="n">
-        <v>8</v>
-      </c>
-      <c r="J344" t="s">
-        <v>21</v>
-      </c>
-      <c r="K344" t="n">
-        <v>1.714</v>
-      </c>
-      <c r="L344" t="s">
-        <v>15</v>
-      </c>
-      <c r="M344" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="1" t="n">
-        <v>44044</v>
-      </c>
-      <c r="B345" t="n">
-        <v>22.3470648847149</v>
-      </c>
-      <c r="C345" t="n">
-        <v>11.5812042602929</v>
-      </c>
-      <c r="D345" t="n">
-        <v>8.44879501469453</v>
-      </c>
-      <c r="E345" t="n">
-        <v>42.5713230271159</v>
-      </c>
-      <c r="F345" t="n">
-        <v>63.5020017552787</v>
-      </c>
-      <c r="G345" t="s">
-        <v>71</v>
-      </c>
-      <c r="H345" t="n">
-        <v>2</v>
-      </c>
-      <c r="I345" t="n">
-        <v>20</v>
-      </c>
-      <c r="J345" t="s">
-        <v>21</v>
-      </c>
-      <c r="K345" t="n">
-        <v>11.123</v>
-      </c>
-      <c r="L345" t="s">
-        <v>72</v>
-      </c>
-      <c r="M345" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="1" t="n">
-        <v>44075</v>
-      </c>
-      <c r="B346" t="n">
-        <v>20.6174297129802</v>
-      </c>
-      <c r="C346" t="n">
-        <v>10.0671962652563</v>
-      </c>
-      <c r="D346" t="n">
-        <v>6.89660162767173</v>
-      </c>
-      <c r="E346" t="n">
-        <v>40.9100697826491</v>
-      </c>
-      <c r="F346" t="n">
-        <v>57.3843648175692</v>
-      </c>
-      <c r="G346" t="s">
-        <v>71</v>
-      </c>
-      <c r="H346" t="n">
-        <v>10</v>
-      </c>
-      <c r="I346" t="n">
-        <v>11</v>
-      </c>
-      <c r="J346" t="s">
-        <v>21</v>
-      </c>
-      <c r="K346" t="n">
-        <v>2.061</v>
-      </c>
-      <c r="L346" t="s">
-        <v>15</v>
-      </c>
-      <c r="M346" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="1" t="n">
-        <v>44105</v>
-      </c>
-      <c r="B347" t="n">
-        <v>20.0533986062767</v>
-      </c>
-      <c r="C347" t="n">
-        <v>9.68429652960064</v>
-      </c>
-      <c r="D347" t="n">
-        <v>6.83922131263951</v>
-      </c>
-      <c r="E347" t="n">
-        <v>40.3351190937772</v>
-      </c>
-      <c r="F347" t="n">
-        <v>59.9731562233223</v>
-      </c>
-      <c r="G347" t="s">
-        <v>71</v>
-      </c>
-      <c r="H347" t="n">
-        <v>6</v>
-      </c>
-      <c r="I347" t="n">
-        <v>14</v>
-      </c>
-      <c r="J347" t="s">
-        <v>21</v>
-      </c>
-      <c r="K347" t="n">
-        <v>3.338</v>
-      </c>
-      <c r="L347" t="s">
-        <v>15</v>
-      </c>
-      <c r="M347" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="1" t="n">
-        <v>44136</v>
-      </c>
-      <c r="B348" t="n">
-        <v>15.9849806864111</v>
-      </c>
-      <c r="C348" t="n">
-        <v>7.4060146347068</v>
-      </c>
-      <c r="D348" t="n">
-        <v>4.75253712028022</v>
-      </c>
-      <c r="E348" t="n">
-        <v>32.5213287989511</v>
-      </c>
-      <c r="F348" t="n">
-        <v>47.9644047596636</v>
-      </c>
-      <c r="G348" t="s">
-        <v>71</v>
-      </c>
-      <c r="H348" t="n">
-        <v>5</v>
-      </c>
-      <c r="I348" t="n">
-        <v>11</v>
-      </c>
-      <c r="J348" t="s">
-        <v>21</v>
-      </c>
-      <c r="K348" t="n">
-        <v>3.193</v>
-      </c>
-      <c r="L348" t="s">
-        <v>15</v>
-      </c>
-      <c r="M348" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="1" t="n">
-        <v>44166</v>
-      </c>
-      <c r="B349" t="n">
-        <v>15.3628491183374</v>
-      </c>
-      <c r="C349" t="n">
-        <v>6.95015806055589</v>
-      </c>
-      <c r="D349" t="n">
-        <v>4.53434692954655</v>
-      </c>
-      <c r="E349" t="n">
-        <v>32.88674146188</v>
-      </c>
-      <c r="F349" t="n">
-        <v>53.5612735374543</v>
-      </c>
-      <c r="G349" t="s">
-        <v>71</v>
-      </c>
-      <c r="H349" t="n">
-        <v>4</v>
-      </c>
-      <c r="I349" t="n">
-        <v>11</v>
-      </c>
-      <c r="J349" t="s">
-        <v>21</v>
-      </c>
-      <c r="K349" t="n">
-        <v>3.834</v>
-      </c>
-      <c r="L349" t="s">
-        <v>15</v>
-      </c>
-      <c r="M349" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="1" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B350" t="n">
-        <v>18.9444531487298</v>
-      </c>
-      <c r="C350" t="n">
-        <v>8.25158624169934</v>
-      </c>
-      <c r="D350" t="n">
-        <v>4.64397205919521</v>
-      </c>
-      <c r="E350" t="n">
-        <v>41.7406681453813</v>
-      </c>
-      <c r="F350" t="n">
-        <v>63.4460393055856</v>
-      </c>
-      <c r="G350" t="s">
-        <v>71</v>
-      </c>
-      <c r="H350" t="n">
-        <v>5</v>
-      </c>
-      <c r="I350" t="n">
-        <v>14</v>
-      </c>
-      <c r="J350" t="s">
-        <v>21</v>
-      </c>
-      <c r="K350" t="n">
-        <v>3.783</v>
-      </c>
-      <c r="L350" t="s">
-        <v>15</v>
-      </c>
-      <c r="M350" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="1" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B351" t="n">
-        <v>17.0029937450822</v>
-      </c>
-      <c r="C351" t="n">
-        <v>7.20214215354212</v>
-      </c>
-      <c r="D351" t="n">
-        <v>4.63304754954789</v>
-      </c>
-      <c r="E351" t="n">
-        <v>40.1732231643186</v>
-      </c>
-      <c r="F351" t="n">
-        <v>62.9917509725906</v>
-      </c>
-      <c r="G351" t="s">
-        <v>71</v>
-      </c>
-      <c r="H351" t="n">
-        <v>2</v>
-      </c>
-      <c r="I351" t="n">
-        <v>15</v>
-      </c>
-      <c r="J351" t="s">
-        <v>21</v>
-      </c>
-      <c r="K351" t="n">
-        <v>8.464</v>
-      </c>
-      <c r="L351" t="s">
-        <v>15</v>
-      </c>
-      <c r="M351" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="1" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B352" t="n">
-        <v>15.2107779556114</v>
-      </c>
-      <c r="C352" t="n">
-        <v>6.28454233489265</v>
-      </c>
-      <c r="D352" t="n">
-        <v>3.9298271861202</v>
-      </c>
-      <c r="E352" t="n">
-        <v>35.8638645420988</v>
-      </c>
-      <c r="F352" t="n">
-        <v>60.5981319433727</v>
-      </c>
-      <c r="G352" t="s">
-        <v>71</v>
-      </c>
-      <c r="H352" t="n">
-        <v>7</v>
-      </c>
-      <c r="I352" t="n">
-        <v>8</v>
-      </c>
-      <c r="J352" t="s">
-        <v>21</v>
-      </c>
-      <c r="K352" t="n">
-        <v>2.171</v>
-      </c>
-      <c r="L352" t="s">
-        <v>15</v>
-      </c>
-      <c r="M352" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="1" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B353" t="n">
-        <v>14.0105496303163</v>
-      </c>
-      <c r="C353" t="n">
-        <v>5.32111426150855</v>
-      </c>
-      <c r="D353" t="n">
-        <v>3.22628230766388</v>
-      </c>
-      <c r="E353" t="n">
-        <v>34.6049597128467</v>
-      </c>
-      <c r="F353" t="n">
-        <v>60.3566025904301</v>
-      </c>
-      <c r="G353" t="s">
-        <v>71</v>
-      </c>
-      <c r="H353" t="n">
-        <v>6</v>
-      </c>
-      <c r="I353" t="n">
-        <v>8</v>
-      </c>
-      <c r="J353" t="s">
-        <v>21</v>
-      </c>
-      <c r="K353" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="L353" t="s">
-        <v>15</v>
-      </c>
-      <c r="M353" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="1" t="n">
-        <v>44317</v>
-      </c>
-      <c r="B354" t="n">
-        <v>14.6505072873711</v>
-      </c>
-      <c r="C354" t="n">
-        <v>5.45924694833327</v>
-      </c>
-      <c r="D354" t="n">
-        <v>3.22311856984902</v>
-      </c>
-      <c r="E354" t="n">
-        <v>39.0232255103081</v>
-      </c>
-      <c r="F354" t="n">
-        <v>68.4350675041942</v>
-      </c>
-      <c r="G354" t="s">
-        <v>71</v>
-      </c>
-      <c r="H354" t="n">
-        <v>6</v>
-      </c>
-      <c r="I354" t="n">
-        <v>9</v>
-      </c>
-      <c r="J354" t="s">
-        <v>21</v>
-      </c>
-      <c r="K354" t="n">
-        <v>2.439</v>
-      </c>
-      <c r="L354" t="s">
-        <v>15</v>
-      </c>
-      <c r="M354" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="1" t="n">
-        <v>44348</v>
-      </c>
-      <c r="B355" t="n">
-        <v>23.1493268482328</v>
-      </c>
-      <c r="C355" t="n">
-        <v>8.82520573747567</v>
-      </c>
-      <c r="D355" t="n">
-        <v>5.15840928229351</v>
-      </c>
-      <c r="E355" t="n">
-        <v>61.3506259403862</v>
-      </c>
-      <c r="F355" t="n">
-        <v>107.114970635299</v>
-      </c>
-      <c r="G355" t="s">
-        <v>71</v>
-      </c>
-      <c r="H355" t="n">
-        <v>8</v>
-      </c>
-      <c r="I355" t="n">
-        <v>15</v>
-      </c>
-      <c r="J355" t="s">
-        <v>21</v>
-      </c>
-      <c r="K355" t="n">
-        <v>2.891</v>
-      </c>
-      <c r="L355" t="s">
-        <v>15</v>
-      </c>
-      <c r="M355" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="1" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B356" t="n">
-        <v>17.3565663307614</v>
-      </c>
-      <c r="C356" t="n">
-        <v>5.92976286774688</v>
-      </c>
-      <c r="D356" t="n">
-        <v>3.52696673909897</v>
-      </c>
-      <c r="E356" t="n">
-        <v>47.5434881138071</v>
-      </c>
-      <c r="F356" t="n">
-        <v>85.4595454566503</v>
-      </c>
-      <c r="G356" t="s">
-        <v>71</v>
-      </c>
-      <c r="H356" t="n">
-        <v>1</v>
-      </c>
-      <c r="I356" t="n">
-        <v>16</v>
-      </c>
-      <c r="J356" t="s">
-        <v>21</v>
-      </c>
-      <c r="K356" t="n">
-        <v>17.195</v>
-      </c>
-      <c r="L356" t="s">
-        <v>72</v>
-      </c>
-      <c r="M356" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="1" t="n">
-        <v>44409</v>
-      </c>
-      <c r="B357" t="n">
-        <v>21.0705411935606</v>
-      </c>
-      <c r="C357" t="n">
-        <v>7.01490282225676</v>
-      </c>
-      <c r="D357" t="n">
-        <v>3.77155617495804</v>
-      </c>
-      <c r="E357" t="n">
-        <v>58.5260726135416</v>
-      </c>
-      <c r="F357" t="n">
-        <v>121.163241294792</v>
-      </c>
-      <c r="G357" t="s">
-        <v>71</v>
-      </c>
-      <c r="H357" t="n">
-        <v>2</v>
-      </c>
-      <c r="I357" t="n">
-        <v>19</v>
-      </c>
-      <c r="J357" t="s">
-        <v>21</v>
-      </c>
-      <c r="K357" t="n">
-        <v>10.488</v>
-      </c>
-      <c r="L357" t="s">
-        <v>72</v>
-      </c>
-      <c r="M357" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="1" t="n">
-        <v>44440</v>
-      </c>
-      <c r="B358" t="n">
-        <v>19.3391890832811</v>
-      </c>
-      <c r="C358" t="n">
-        <v>6.41139304027444</v>
-      </c>
-      <c r="D358" t="n">
-        <v>3.3134758362501</v>
-      </c>
-      <c r="E358" t="n">
-        <v>54.3046075876394</v>
-      </c>
-      <c r="F358" t="n">
-        <v>108.673719722554</v>
-      </c>
-      <c r="G358" t="s">
-        <v>71</v>
-      </c>
-      <c r="H358" t="n">
-        <v>2</v>
-      </c>
-      <c r="I358" t="n">
-        <v>17</v>
-      </c>
-      <c r="J358" t="s">
-        <v>21</v>
-      </c>
-      <c r="K358" t="n">
-        <v>9.626</v>
-      </c>
-      <c r="L358" t="s">
-        <v>15</v>
-      </c>
-      <c r="M358" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B359" t="n">
-        <v>18.8370851358006</v>
-      </c>
-      <c r="C359" t="n">
-        <v>5.75308321330371</v>
-      </c>
-      <c r="D359" t="n">
-        <v>3.44167215316549</v>
-      </c>
-      <c r="E359" t="n">
-        <v>59.0364974418511</v>
-      </c>
-      <c r="F359" t="n">
-        <v>100.269000798049</v>
-      </c>
-      <c r="G359" t="s">
-        <v>71</v>
-      </c>
-      <c r="H359" t="n">
-        <v>3</v>
-      </c>
-      <c r="I359" t="n">
-        <v>16</v>
-      </c>
-      <c r="J359" t="s">
-        <v>21</v>
-      </c>
-      <c r="K359" t="n">
-        <v>6.261</v>
-      </c>
-      <c r="L359" t="s">
-        <v>15</v>
-      </c>
-      <c r="M359" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="1" t="n">
-        <v>44501</v>
-      </c>
-      <c r="B360" t="n">
-        <v>15.3399704811315</v>
-      </c>
-      <c r="C360" t="n">
-        <v>4.78869927520514</v>
-      </c>
-      <c r="D360" t="n">
-        <v>2.37178520004549</v>
-      </c>
-      <c r="E360" t="n">
-        <v>47.4753450092231</v>
-      </c>
-      <c r="F360" t="n">
-        <v>88.1812948753735</v>
-      </c>
-      <c r="G360" t="s">
-        <v>71</v>
-      </c>
-      <c r="H360" t="n">
-        <v>5</v>
-      </c>
-      <c r="I360" t="n">
-        <v>10</v>
-      </c>
-      <c r="J360" t="s">
-        <v>21</v>
-      </c>
-      <c r="K360" t="n">
-        <v>3.064</v>
-      </c>
-      <c r="L360" t="s">
-        <v>15</v>
-      </c>
-      <c r="M360" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="1" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B361" t="n">
-        <v>14.3988396343311</v>
-      </c>
-      <c r="C361" t="n">
-        <v>4.15809911817613</v>
-      </c>
-      <c r="D361" t="n">
-        <v>2.55328159489838</v>
-      </c>
-      <c r="E361" t="n">
-        <v>47.8458259651512</v>
-      </c>
-      <c r="F361" t="n">
-        <v>93.3287189199502</v>
-      </c>
-      <c r="G361" t="s">
-        <v>71</v>
-      </c>
-      <c r="H361" t="n">
-        <v>3</v>
-      </c>
-      <c r="I361" t="n">
-        <v>11</v>
-      </c>
-      <c r="J361" t="s">
-        <v>21</v>
-      </c>
-      <c r="K361" t="n">
-        <v>4.787</v>
-      </c>
-      <c r="L361" t="s">
-        <v>15</v>
-      </c>
-      <c r="M361" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="1" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B362" t="n">
-        <v>17.4396908309706</v>
-      </c>
-      <c r="C362" t="n">
-        <v>4.8163482874992</v>
-      </c>
-      <c r="D362" t="n">
-        <v>2.34288164783947</v>
-      </c>
-      <c r="E362" t="n">
-        <v>59.5126690675845</v>
-      </c>
-      <c r="F362" t="n">
-        <v>112.179065818022</v>
-      </c>
-      <c r="G362" t="s">
-        <v>71</v>
-      </c>
-      <c r="H362" t="n">
-        <v>7</v>
-      </c>
-      <c r="I362" t="n">
-        <v>10</v>
-      </c>
-      <c r="J362" t="s">
-        <v>21</v>
-      </c>
-      <c r="K362" t="n">
-        <v>2.489</v>
-      </c>
-      <c r="L362" t="s">
-        <v>15</v>
-      </c>
-      <c r="M362" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B363" t="n">
-        <v>15.6944452574092</v>
-      </c>
-      <c r="C363" t="n">
-        <v>4.56231651179814</v>
-      </c>
-      <c r="D363" t="n">
-        <v>2.20197087025875</v>
-      </c>
-      <c r="E363" t="n">
-        <v>54.9354376079202</v>
-      </c>
-      <c r="F363" t="n">
-        <v>98.7227874543453</v>
-      </c>
-      <c r="G363" t="s">
-        <v>71</v>
-      </c>
-      <c r="H363" t="n">
-        <v>4</v>
-      </c>
-      <c r="I363" t="n">
-        <v>12</v>
-      </c>
-      <c r="J363" t="s">
-        <v>21</v>
-      </c>
-      <c r="K363" t="n">
-        <v>3.916</v>
-      </c>
-      <c r="L363" t="s">
-        <v>15</v>
-      </c>
-      <c r="M363" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="B364" t="n">
-        <v>14.3429534327638</v>
-      </c>
-      <c r="C364" t="n">
-        <v>3.69357673952375</v>
-      </c>
-      <c r="D364" t="n">
-        <v>1.9373839547109</v>
-      </c>
-      <c r="E364" t="n">
-        <v>55.1470508725407</v>
-      </c>
-      <c r="F364" t="n">
-        <v>106.157406585251</v>
-      </c>
-      <c r="G364" t="s">
-        <v>71</v>
-      </c>
-      <c r="H364" t="n">
-        <v>5</v>
-      </c>
-      <c r="I364" t="n">
-        <v>9</v>
-      </c>
-      <c r="J364" t="s">
-        <v>21</v>
-      </c>
-      <c r="K364" t="n">
-        <v>2.865</v>
-      </c>
-      <c r="L364" t="s">
-        <v>15</v>
-      </c>
-      <c r="M364" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B365" t="n">
-        <v>12.9734850899388</v>
-      </c>
-      <c r="C365" t="n">
-        <v>3.10663859400096</v>
-      </c>
-      <c r="D365" t="n">
-        <v>1.42886305233177</v>
-      </c>
-      <c r="E365" t="n">
-        <v>51.9742026507719</v>
-      </c>
-      <c r="F365" t="n">
-        <v>95.6622571225152</v>
-      </c>
-      <c r="G365" t="s">
-        <v>71</v>
-      </c>
-      <c r="H365" t="n">
-        <v>4</v>
-      </c>
-      <c r="I365" t="n">
-        <v>9</v>
-      </c>
-      <c r="J365" t="s">
-        <v>21</v>
-      </c>
-      <c r="K365" t="n">
-        <v>3.238</v>
-      </c>
-      <c r="L365" t="s">
-        <v>15</v>
-      </c>
-      <c r="M365" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="B366" t="n">
-        <v>13.7477354821042</v>
-      </c>
-      <c r="C366" t="n">
-        <v>3.35814498649638</v>
-      </c>
-      <c r="D366" t="n">
-        <v>1.5537464686355</v>
-      </c>
-      <c r="E366" t="n">
-        <v>53.2173593987792</v>
-      </c>
-      <c r="F366" t="n">
-        <v>122.523610882653</v>
-      </c>
-      <c r="G366" t="s">
-        <v>71</v>
-      </c>
-      <c r="H366" t="n">
-        <v>9</v>
-      </c>
-      <c r="I366" t="n">
-        <v>5</v>
-      </c>
-      <c r="J366" t="s">
-        <v>21</v>
-      </c>
-      <c r="K366" t="n">
-        <v>1.527</v>
-      </c>
-      <c r="L366" t="s">
-        <v>15</v>
-      </c>
-      <c r="M366" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B367" t="n">
-        <v>21.8429357159462</v>
-      </c>
-      <c r="C367" t="n">
-        <v>5.05979588988962</v>
-      </c>
-      <c r="D367" t="n">
-        <v>2.41410163556456</v>
-      </c>
-      <c r="E367" t="n">
-        <v>92.0948688028569</v>
-      </c>
-      <c r="F367" t="n">
-        <v>239.016037759518</v>
-      </c>
-      <c r="G367" t="s">
-        <v>71</v>
-      </c>
-      <c r="H367" t="n">
-        <v>10</v>
-      </c>
-      <c r="I367" t="n">
-        <v>12</v>
-      </c>
-      <c r="J367" t="s">
-        <v>21</v>
-      </c>
-      <c r="K367" t="n">
-        <v>2.183</v>
-      </c>
-      <c r="L367" t="s">
-        <v>15</v>
-      </c>
-      <c r="M367" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" s="1" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B368" t="n">
-        <v>16.0220571192012</v>
-      </c>
-      <c r="C368" t="n">
-        <v>3.67549047392506</v>
-      </c>
-      <c r="D368" t="n">
-        <v>1.44357898852975</v>
-      </c>
-      <c r="E368" t="n">
-        <v>67.5750936951491</v>
-      </c>
-      <c r="F368" t="n">
-        <v>158.819543629103</v>
-      </c>
-      <c r="G368" t="s">
-        <v>71</v>
-      </c>
-      <c r="H368" t="n">
-        <v>16</v>
-      </c>
-      <c r="I368" t="n">
-        <v>0</v>
-      </c>
-      <c r="J368" t="s">
-        <v>21</v>
-      </c>
-      <c r="K368" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="L368" t="s">
-        <v>15</v>
-      </c>
-      <c r="M368" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="B369" t="n">
-        <v>19.1490279679091</v>
-      </c>
-      <c r="C369" t="n">
-        <v>4.30311981800248</v>
-      </c>
-      <c r="D369" t="n">
-        <v>1.94154971001952</v>
-      </c>
-      <c r="E369" t="n">
-        <v>81.9672449818801</v>
-      </c>
-      <c r="F369" t="n">
-        <v>191.872872524238</v>
-      </c>
-      <c r="G369" t="s">
-        <v>71</v>
-      </c>
-      <c r="H369" t="n">
-        <v>6</v>
-      </c>
-      <c r="I369" t="n">
-        <v>13</v>
-      </c>
-      <c r="J369" t="s">
-        <v>21</v>
-      </c>
-      <c r="K369" t="n">
-        <v>3.188</v>
-      </c>
-      <c r="L369" t="s">
-        <v>15</v>
-      </c>
-      <c r="M369" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="1" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B370" t="n">
-        <v>17.9128171393635</v>
-      </c>
-      <c r="C370" t="n">
-        <v>3.87764135992064</v>
-      </c>
-      <c r="D370" t="n">
-        <v>1.39720306022046</v>
-      </c>
-      <c r="E370" t="n">
-        <v>82.9675486945309</v>
-      </c>
-      <c r="F370" t="n">
-        <v>196.756124962549</v>
-      </c>
-      <c r="G370" t="s">
-        <v>71</v>
-      </c>
-      <c r="H370" t="n">
-        <v>11</v>
-      </c>
-      <c r="I370" t="n">
-        <v>7</v>
-      </c>
-      <c r="J370" t="s">
-        <v>21</v>
-      </c>
-      <c r="K370" t="n">
-        <v>1.628</v>
-      </c>
-      <c r="L370" t="s">
-        <v>15</v>
-      </c>
-      <c r="M370" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B371" t="n">
-        <v>17.7924502072416</v>
-      </c>
-      <c r="C371" t="n">
-        <v>3.68699983478089</v>
-      </c>
-      <c r="D371" t="n">
-        <v>1.29683726224373</v>
-      </c>
-      <c r="E371" t="n">
-        <v>85.2158542579143</v>
-      </c>
-      <c r="F371" t="n">
-        <v>207.318640606205</v>
-      </c>
-      <c r="G371" t="s">
-        <v>71</v>
-      </c>
-      <c r="H371" t="n">
-        <v>10</v>
-      </c>
-      <c r="I371" t="n">
-        <v>8</v>
-      </c>
-      <c r="J371" t="s">
-        <v>21</v>
-      </c>
-      <c r="K371" t="n">
-        <v>1.778</v>
-      </c>
-      <c r="L371" t="s">
-        <v>15</v>
-      </c>
-      <c r="M371" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B372" t="n">
-        <v>14.3669814401923</v>
-      </c>
-      <c r="C372" t="n">
-        <v>2.84265229529408</v>
-      </c>
-      <c r="D372" t="n">
-        <v>1.04491150058442</v>
-      </c>
-      <c r="E372" t="n">
-        <v>70.975667524915</v>
-      </c>
-      <c r="F372" t="n">
-        <v>182.981573119332</v>
-      </c>
-      <c r="G372" t="s">
-        <v>71</v>
-      </c>
-      <c r="H372" t="n">
-        <v>5</v>
-      </c>
-      <c r="I372" t="n">
-        <v>9</v>
-      </c>
-      <c r="J372" t="s">
-        <v>21</v>
-      </c>
-      <c r="K372" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="L372" t="s">
-        <v>15</v>
-      </c>
-      <c r="M372" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B373" t="n">
-        <v>13.6330595757188</v>
-      </c>
-      <c r="C373" t="n">
-        <v>2.69406423654485</v>
-      </c>
-      <c r="D373" t="n">
-        <v>0.913235196895162</v>
-      </c>
-      <c r="E373" t="n">
-        <v>69.4981265422255</v>
-      </c>
-      <c r="F373" t="n">
-        <v>207.92991806106</v>
-      </c>
-      <c r="G373" t="s">
-        <v>71</v>
-      </c>
-      <c r="H373" t="n">
-        <v>4</v>
-      </c>
-      <c r="I373" t="n">
-        <v>10</v>
-      </c>
-      <c r="J373" t="s">
-        <v>21</v>
-      </c>
-      <c r="K373" t="n">
-        <v>3.402</v>
-      </c>
-      <c r="L373" t="s">
-        <v>15</v>
-      </c>
-      <c r="M373" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B374" t="n">
-        <v>16.2702555341463</v>
-      </c>
-      <c r="C374" t="n">
-        <v>2.71278340318857</v>
-      </c>
-      <c r="D374" t="n">
-        <v>0.966007541988561</v>
-      </c>
-      <c r="E374" t="n">
-        <v>88.5295067384893</v>
-      </c>
-      <c r="F374" t="n">
-        <v>216.952895551325</v>
-      </c>
-      <c r="G374" t="s">
-        <v>71</v>
-      </c>
-      <c r="H374" t="n">
-        <v>14</v>
-      </c>
-      <c r="I374" t="n">
-        <v>2</v>
-      </c>
-      <c r="J374" t="s">
-        <v>21</v>
-      </c>
-      <c r="K374" t="n">
-        <v>1.162</v>
-      </c>
-      <c r="L374" t="s">
-        <v>15</v>
-      </c>
-      <c r="M374" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" s="1" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B375" t="n">
-        <v>15.1333891534268</v>
-      </c>
-      <c r="C375" t="n">
-        <v>2.79386311629882</v>
-      </c>
-      <c r="D375" t="n">
-        <v>0.879368605292988</v>
-      </c>
-      <c r="E375" t="n">
-        <v>87.3770784426067</v>
-      </c>
-      <c r="F375" t="n">
-        <v>241.90633821392</v>
-      </c>
-      <c r="G375" t="s">
-        <v>71</v>
-      </c>
-      <c r="H375" t="n">
-        <v>18</v>
-      </c>
-      <c r="I375" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J375" t="s">
-        <v>14</v>
-      </c>
-      <c r="K375" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="L375" t="s">
-        <v>15</v>
-      </c>
-      <c r="M375" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" s="1" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B376" t="n">
-        <v>13.7517258553829</v>
-      </c>
-      <c r="C376" t="n">
-        <v>2.24315802224203</v>
-      </c>
-      <c r="D376" t="n">
-        <v>0.692346152390148</v>
-      </c>
-      <c r="E376" t="n">
-        <v>79.9794637289388</v>
-      </c>
-      <c r="F376" t="n">
-        <v>207.797400250394</v>
-      </c>
-      <c r="G376" t="s">
-        <v>71</v>
-      </c>
-      <c r="H376" t="n">
-        <v>24</v>
-      </c>
-      <c r="I376" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J376" t="s">
-        <v>14</v>
-      </c>
-      <c r="K376" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="L376" t="s">
-        <v>15</v>
-      </c>
-      <c r="M376" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B377" t="n">
-        <v>12.4769499217179</v>
-      </c>
-      <c r="C377" t="n">
-        <v>1.74318177538909</v>
-      </c>
-      <c r="D377" t="n">
-        <v>0.549432321062904</v>
-      </c>
-      <c r="E377" t="n">
-        <v>82.6892600696246</v>
-      </c>
-      <c r="F377" t="n">
-        <v>227.741652413548</v>
-      </c>
-      <c r="G377" t="s">
-        <v>71</v>
-      </c>
-      <c r="H377" t="n">
-        <v>10</v>
-      </c>
-      <c r="I377" t="n">
-        <v>2</v>
-      </c>
-      <c r="J377" t="s">
-        <v>21</v>
-      </c>
-      <c r="K377" t="n">
-        <v>1.247</v>
-      </c>
-      <c r="L377" t="s">
-        <v>15</v>
-      </c>
-      <c r="M377" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B378" t="n">
-        <v>13.1469661950133</v>
-      </c>
-      <c r="C378" t="n">
-        <v>2.05485932090638</v>
-      </c>
-      <c r="D378" t="n">
-        <v>0.702343719251798</v>
-      </c>
-      <c r="E378" t="n">
-        <v>83.167841308236</v>
-      </c>
-      <c r="F378" t="n">
-        <v>250.4584480969</v>
-      </c>
-      <c r="G378" t="s">
-        <v>71</v>
-      </c>
-      <c r="H378" t="n">
-        <v>13</v>
-      </c>
-      <c r="I378" t="n">
-        <v>0</v>
-      </c>
-      <c r="J378" t="s">
-        <v>21</v>
-      </c>
-      <c r="K378" t="n">
-        <v>1.011</v>
-      </c>
-      <c r="L378" t="s">
-        <v>15</v>
-      </c>
-      <c r="M378" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B379" t="n">
-        <v>20.81963534492</v>
-      </c>
-      <c r="C379" t="n">
-        <v>2.83638864132277</v>
-      </c>
-      <c r="D379" t="n">
-        <v>0.77870642013598</v>
-      </c>
-      <c r="E379" t="n">
-        <v>152.509039014087</v>
-      </c>
-      <c r="F379" t="n">
-        <v>378.458087253637</v>
-      </c>
-      <c r="G379" t="s">
-        <v>71</v>
-      </c>
-      <c r="H379" t="n">
-        <v>26</v>
-      </c>
-      <c r="I379" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J379" t="s">
-        <v>14</v>
-      </c>
-      <c r="K379" t="n">
-        <v>0.801</v>
-      </c>
-      <c r="L379" t="s">
-        <v>15</v>
-      </c>
-      <c r="M379" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" s="1" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B380" t="n">
-        <v>15.4866014503114</v>
-      </c>
-      <c r="C380" t="n">
-        <v>2.11317483970343</v>
-      </c>
-      <c r="D380" t="n">
-        <v>0.57135483778272</v>
-      </c>
-      <c r="E380" t="n">
-        <v>108.980686677416</v>
-      </c>
-      <c r="F380" t="n">
-        <v>278.826781562015</v>
-      </c>
-      <c r="G380" t="s">
-        <v>71</v>
-      </c>
-      <c r="H380" t="n">
-        <v>16</v>
-      </c>
-      <c r="I380" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J380" t="s">
-        <v>14</v>
-      </c>
-      <c r="K380" t="n">
-        <v>0.968</v>
-      </c>
-      <c r="L380" t="s">
-        <v>15</v>
-      </c>
-      <c r="M380" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B381" t="n">
-        <v>18.8507543271638</v>
-      </c>
-      <c r="C381" t="n">
-        <v>2.4232724267773</v>
-      </c>
-      <c r="D381" t="n">
-        <v>0.682305929253203</v>
-      </c>
-      <c r="E381" t="n">
-        <v>136.680376227079</v>
-      </c>
-      <c r="F381" t="n">
-        <v>391.17146940429</v>
-      </c>
-      <c r="G381" t="s">
-        <v>71</v>
-      </c>
-      <c r="H381" t="n">
-        <v>16</v>
-      </c>
-      <c r="I381" t="n">
-        <v>3</v>
-      </c>
-      <c r="J381" t="s">
-        <v>21</v>
-      </c>
-      <c r="K381" t="n">
-        <v>1.178</v>
-      </c>
-      <c r="L381" t="s">
-        <v>15</v>
-      </c>
-      <c r="M381" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B382" t="n">
-        <v>17.4042456432152</v>
-      </c>
-      <c r="C382" t="n">
-        <v>2.11473551743783</v>
-      </c>
-      <c r="D382" t="n">
-        <v>0.54322866855609</v>
-      </c>
-      <c r="E382" t="n">
-        <v>129.394543996289</v>
-      </c>
-      <c r="F382" t="n">
-        <v>396.148912151985</v>
-      </c>
-      <c r="G382" t="s">
-        <v>71</v>
-      </c>
-      <c r="H382" t="n">
-        <v>8</v>
-      </c>
-      <c r="I382" t="n">
-        <v>9</v>
-      </c>
-      <c r="J382" t="s">
-        <v>21</v>
-      </c>
-      <c r="K382" t="n">
-        <v>2.174</v>
-      </c>
-      <c r="L382" t="s">
-        <v>15</v>
-      </c>
-      <c r="M382" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="1" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B383" t="n">
-        <v>16.9011561257076</v>
-      </c>
-      <c r="C383" t="n">
-        <v>2.03365050347459</v>
-      </c>
-      <c r="D383" t="n">
-        <v>0.602452779017483</v>
-      </c>
-      <c r="E383" t="n">
-        <v>120.605767029023</v>
-      </c>
-      <c r="F383" t="n">
-        <v>422.079510826369</v>
-      </c>
-      <c r="G383" t="s">
-        <v>71</v>
-      </c>
-      <c r="H383" t="n">
-        <v>23</v>
-      </c>
-      <c r="I383" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J383" t="s">
-        <v>14</v>
-      </c>
-      <c r="K383" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="L383" t="s">
-        <v>15</v>
-      </c>
-      <c r="M383" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="1" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B384" t="n">
-        <v>13.7168013492874</v>
-      </c>
-      <c r="C384" t="n">
-        <v>1.55172052581933</v>
-      </c>
-      <c r="D384" t="n">
-        <v>0.396236768694597</v>
-      </c>
-      <c r="E384" t="n">
-        <v>102.934709744496</v>
-      </c>
-      <c r="F384" t="n">
-        <v>363.669353246572</v>
-      </c>
-      <c r="G384" t="s">
-        <v>71</v>
-      </c>
-      <c r="H384" t="n">
-        <v>20</v>
-      </c>
-      <c r="I384" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J384" t="s">
-        <v>14</v>
-      </c>
-      <c r="K384" t="n">
-        <v>0.686</v>
-      </c>
-      <c r="L384" t="s">
-        <v>15</v>
-      </c>
-      <c r="M384" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B385" t="n">
-        <v>12.9253274123683</v>
-      </c>
-      <c r="C385" t="n">
-        <v>1.32564308357073</v>
-      </c>
-      <c r="D385" t="n">
-        <v>0.378490788739163</v>
-      </c>
-      <c r="E385" t="n">
-        <v>114.77962720944</v>
-      </c>
-      <c r="F385" t="n">
-        <v>370.504376144594</v>
-      </c>
-      <c r="G385" t="s">
-        <v>71</v>
-      </c>
-      <c r="H385" t="n">
-        <v>17</v>
-      </c>
-      <c r="I385" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J385" t="s">
-        <v>14</v>
-      </c>
-      <c r="K385" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L385" t="s">
-        <v>15</v>
-      </c>
-      <c r="M385" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="B386" t="n">
-        <v>0.0124304187311544</v>
-      </c>
-      <c r="C386" t="n">
-        <v>0.000402531095245496</v>
-      </c>
-      <c r="D386" t="n">
-        <v>0.0000578977449218938</v>
-      </c>
-      <c r="E386" t="n">
-        <v>0.327564890384772</v>
-      </c>
-      <c r="F386" t="n">
-        <v>1.96928088033984</v>
-      </c>
-      <c r="G386" t="s">
-        <v>73</v>
-      </c>
-      <c r="H386" t="n">
-        <v>0</v>
-      </c>
-      <c r="I386" t="n">
-        <v>0</v>
-      </c>
-      <c r="J386" t="s">
-        <v>21</v>
-      </c>
-      <c r="K386" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="L386" t="s">
-        <v>15</v>
-      </c>
-      <c r="M386" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="1" t="n">
-        <v>43862</v>
-      </c>
-      <c r="B387" t="n">
-        <v>0.0188443776708213</v>
-      </c>
-      <c r="C387" t="n">
-        <v>0.000486021652485674</v>
-      </c>
-      <c r="D387" t="n">
-        <v>0.000075826599059203</v>
-      </c>
-      <c r="E387" t="n">
-        <v>0.540418896416695</v>
-      </c>
-      <c r="F387" t="n">
-        <v>4.07118530553264</v>
-      </c>
-      <c r="G387" t="s">
-        <v>73</v>
-      </c>
-      <c r="H387" t="n">
-        <v>0</v>
-      </c>
-      <c r="I387" t="n">
-        <v>0</v>
-      </c>
-      <c r="J387" t="s">
-        <v>21</v>
-      </c>
-      <c r="K387" t="n">
-        <v>2.884</v>
-      </c>
-      <c r="L387" t="s">
-        <v>15</v>
-      </c>
-      <c r="M387" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="B388" t="n">
-        <v>0.0290855491559486</v>
-      </c>
-      <c r="C388" t="n">
-        <v>0.000543957345861066</v>
-      </c>
-      <c r="D388" t="n">
-        <v>0.0000685591904069827</v>
-      </c>
-      <c r="E388" t="n">
-        <v>1.50458480028598</v>
-      </c>
-      <c r="F388" t="n">
-        <v>9.52373107527463</v>
-      </c>
-      <c r="G388" t="s">
-        <v>73</v>
-      </c>
-      <c r="H388" t="n">
-        <v>0</v>
-      </c>
-      <c r="I388" t="n">
-        <v>0</v>
-      </c>
-      <c r="J388" t="s">
-        <v>21</v>
-      </c>
-      <c r="K388" t="n">
-        <v>3.909</v>
-      </c>
-      <c r="L388" t="s">
-        <v>15</v>
-      </c>
-      <c r="M388" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" s="1" t="n">
-        <v>43922</v>
-      </c>
-      <c r="B389" t="n">
-        <v>0.00962983012533054</v>
-      </c>
-      <c r="C389" t="n">
-        <v>0.000098953340112966</v>
-      </c>
-      <c r="D389" t="n">
-        <v>0.0000146600445794263</v>
-      </c>
-      <c r="E389" t="n">
-        <v>0.691529806202938</v>
-      </c>
-      <c r="F389" t="n">
-        <v>4.20954892530236</v>
-      </c>
-      <c r="G389" t="s">
-        <v>73</v>
-      </c>
-      <c r="H389" t="n">
-        <v>1</v>
-      </c>
-      <c r="I389" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J389" t="s">
-        <v>14</v>
-      </c>
-      <c r="K389" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L389" t="s">
-        <v>15</v>
-      </c>
-      <c r="M389" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="B390" t="n">
-        <v>0.0228664022039343</v>
-      </c>
-      <c r="C390" t="n">
-        <v>0.000329082491057206</v>
-      </c>
-      <c r="D390" t="n">
-        <v>0.0000237906030548703</v>
-      </c>
-      <c r="E390" t="n">
-        <v>2.08603864671333</v>
-      </c>
-      <c r="F390" t="n">
-        <v>21.6425273285186</v>
-      </c>
-      <c r="G390" t="s">
-        <v>73</v>
-      </c>
-      <c r="H390" t="n">
-        <v>0</v>
-      </c>
-      <c r="I390" t="n">
-        <v>0</v>
-      </c>
-      <c r="J390" t="s">
-        <v>21</v>
-      </c>
-      <c r="K390" t="n">
-        <v>3.287</v>
-      </c>
-      <c r="L390" t="s">
-        <v>15</v>
-      </c>
-      <c r="M390" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" s="1" t="n">
-        <v>43983</v>
-      </c>
-      <c r="B391" t="n">
-        <v>0.0115636270261245</v>
-      </c>
-      <c r="C391" t="n">
-        <v>0.0000778388426901796</v>
-      </c>
-      <c r="D391" t="n">
-        <v>0.00000532974140546046</v>
-      </c>
-      <c r="E391" t="n">
-        <v>1.15304033138884</v>
-      </c>
-      <c r="F391" t="n">
-        <v>16.2886895638123</v>
-      </c>
-      <c r="G391" t="s">
-        <v>73</v>
-      </c>
-      <c r="H391" t="n">
-        <v>0</v>
-      </c>
-      <c r="I391" t="n">
-        <v>0</v>
-      </c>
-      <c r="J391" t="s">
-        <v>21</v>
-      </c>
-      <c r="K391" t="n">
-        <v>2.156</v>
-      </c>
-      <c r="L391" t="s">
-        <v>15</v>
-      </c>
-      <c r="M391" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="1" t="n">
-        <v>44013</v>
-      </c>
-      <c r="B392" t="n">
-        <v>0.00868577035793208</v>
-      </c>
-      <c r="C392" t="n">
-        <v>0.0000729112819609523</v>
-      </c>
-      <c r="D392" t="n">
-        <v>0.00000375772441845863</v>
-      </c>
-      <c r="E392" t="n">
-        <v>1.27227970189912</v>
-      </c>
-      <c r="F392" t="n">
-        <v>11.8615699653643</v>
-      </c>
-      <c r="G392" t="s">
-        <v>73</v>
-      </c>
-      <c r="H392" t="n">
-        <v>0</v>
-      </c>
-      <c r="I392" t="n">
-        <v>0</v>
-      </c>
-      <c r="J392" t="s">
-        <v>21</v>
-      </c>
-      <c r="K392" t="n">
-        <v>1.869</v>
-      </c>
-      <c r="L392" t="s">
-        <v>15</v>
-      </c>
-      <c r="M392" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" s="1" t="n">
-        <v>44044</v>
-      </c>
-      <c r="B393" t="n">
-        <v>0.00985722002779512</v>
-      </c>
-      <c r="C393" t="n">
-        <v>0.0000528422340675555</v>
-      </c>
-      <c r="D393" t="n">
-        <v>0.00000175094309151505</v>
-      </c>
-      <c r="E393" t="n">
-        <v>1.71044554078837</v>
-      </c>
-      <c r="F393" t="n">
-        <v>20.5398306805355</v>
-      </c>
-      <c r="G393" t="s">
-        <v>73</v>
-      </c>
-      <c r="H393" t="n">
-        <v>2</v>
-      </c>
-      <c r="I393" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J393" t="s">
-        <v>14</v>
-      </c>
-      <c r="K393" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L393" t="s">
-        <v>15</v>
-      </c>
-      <c r="M393" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" s="1" t="n">
-        <v>44075</v>
-      </c>
-      <c r="B394" t="n">
-        <v>0.0288033542786493</v>
-      </c>
-      <c r="C394" t="n">
-        <v>0.0000885603011026562</v>
-      </c>
-      <c r="D394" t="n">
-        <v>0.00000399380213031638</v>
-      </c>
-      <c r="E394" t="n">
-        <v>6.8413960583004</v>
-      </c>
-      <c r="F394" t="n">
-        <v>94.9816181674671</v>
-      </c>
-      <c r="G394" t="s">
-        <v>73</v>
-      </c>
-      <c r="H394" t="n">
-        <v>0</v>
-      </c>
-      <c r="I394" t="n">
-        <v>0</v>
-      </c>
-      <c r="J394" t="s">
-        <v>21</v>
-      </c>
-      <c r="K394" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="L394" t="s">
-        <v>15</v>
-      </c>
-      <c r="M394" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" s="1" t="n">
-        <v>44105</v>
-      </c>
-      <c r="B395" t="n">
-        <v>0.0380485360106994</v>
-      </c>
-      <c r="C395" t="n">
-        <v>0.000151103607212698</v>
-      </c>
-      <c r="D395" t="n">
-        <v>0.00000606779142208761</v>
-      </c>
-      <c r="E395" t="n">
-        <v>10.674219063611</v>
-      </c>
-      <c r="F395" t="n">
-        <v>259.326569739203</v>
-      </c>
-      <c r="G395" t="s">
-        <v>73</v>
-      </c>
-      <c r="H395" t="n">
-        <v>1</v>
-      </c>
-      <c r="I395" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J395" t="s">
-        <v>14</v>
-      </c>
-      <c r="K395" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="L395" t="s">
-        <v>15</v>
-      </c>
-      <c r="M395" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="1" t="n">
-        <v>44136</v>
-      </c>
-      <c r="B396" t="n">
-        <v>0.00909304025245779</v>
-      </c>
-      <c r="C396" t="n">
-        <v>0.0000225009674199531</v>
-      </c>
-      <c r="D396" t="n">
-        <v>0.000000624986838969692</v>
-      </c>
-      <c r="E396" t="n">
-        <v>3.97805207187632</v>
-      </c>
-      <c r="F396" t="n">
-        <v>126.160255973566</v>
-      </c>
-      <c r="G396" t="s">
-        <v>73</v>
-      </c>
-      <c r="H396" t="n">
-        <v>1</v>
-      </c>
-      <c r="I396" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J396" t="s">
-        <v>14</v>
-      </c>
-      <c r="K396" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L396" t="s">
-        <v>15</v>
-      </c>
-      <c r="M396" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="1" t="n">
-        <v>44166</v>
-      </c>
-      <c r="B397" t="n">
-        <v>0.00757836650157995</v>
-      </c>
-      <c r="C397" t="n">
-        <v>0.0000124300776646592</v>
-      </c>
-      <c r="D397" t="n">
-        <v>0.000000199453653200543</v>
-      </c>
-      <c r="E397" t="n">
-        <v>3.42844237564896</v>
-      </c>
-      <c r="F397" t="n">
-        <v>52.7471777503511</v>
-      </c>
-      <c r="G397" t="s">
-        <v>73</v>
-      </c>
-      <c r="H397" t="n">
-        <v>0</v>
-      </c>
-      <c r="I397" t="n">
-        <v>0</v>
-      </c>
-      <c r="J397" t="s">
-        <v>21</v>
-      </c>
-      <c r="K397" t="n">
-        <v>1.758</v>
-      </c>
-      <c r="L397" t="s">
-        <v>15</v>
-      </c>
-      <c r="M397" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" s="1" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B398" t="n">
-        <v>0.00555919437987639</v>
-      </c>
-      <c r="C398" t="n">
-        <v>0.00000735047563197952</v>
-      </c>
-      <c r="D398" t="n">
-        <v>0.0000000959230047000446</v>
-      </c>
-      <c r="E398" t="n">
-        <v>3.48808041568735</v>
-      </c>
-      <c r="F398" t="n">
-        <v>179.336238630108</v>
-      </c>
-      <c r="G398" t="s">
-        <v>73</v>
-      </c>
-      <c r="H398" t="n">
-        <v>0</v>
-      </c>
-      <c r="I398" t="n">
-        <v>0</v>
-      </c>
-      <c r="J398" t="s">
-        <v>21</v>
-      </c>
-      <c r="K398" t="n">
-        <v>1.556</v>
-      </c>
-      <c r="L398" t="s">
-        <v>15</v>
-      </c>
-      <c r="M398" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" s="1" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B399" t="n">
-        <v>0.00686159507510251</v>
-      </c>
-      <c r="C399" t="n">
-        <v>0.00000504329794920489</v>
-      </c>
-      <c r="D399" t="n">
-        <v>0.000000131608670578212</v>
-      </c>
-      <c r="E399" t="n">
-        <v>7.74887883875475</v>
-      </c>
-      <c r="F399" t="n">
-        <v>245.147756505863</v>
-      </c>
-      <c r="G399" t="s">
-        <v>73</v>
-      </c>
-      <c r="H399" t="n">
-        <v>0</v>
-      </c>
-      <c r="I399" t="n">
-        <v>0</v>
-      </c>
-      <c r="J399" t="s">
-        <v>21</v>
-      </c>
-      <c r="K399" t="n">
-        <v>1.686</v>
-      </c>
-      <c r="L399" t="s">
-        <v>15</v>
-      </c>
-      <c r="M399" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" s="1" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B400" t="n">
-        <v>0.0135708843591851</v>
-      </c>
-      <c r="C400" t="n">
-        <v>0.00000885181285855747</v>
-      </c>
-      <c r="D400" t="n">
-        <v>0.000000155288205983255</v>
-      </c>
-      <c r="E400" t="n">
-        <v>13.9253663730779</v>
-      </c>
-      <c r="F400" t="n">
-        <v>954.174436325748</v>
-      </c>
-      <c r="G400" t="s">
-        <v>73</v>
-      </c>
-      <c r="H400" t="n">
-        <v>0</v>
-      </c>
-      <c r="I400" t="n">
-        <v>0</v>
-      </c>
-      <c r="J400" t="s">
-        <v>21</v>
-      </c>
-      <c r="K400" t="n">
-        <v>2.357</v>
-      </c>
-      <c r="L400" t="s">
-        <v>15</v>
-      </c>
-      <c r="M400" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" s="1" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B401" t="n">
-        <v>0.00386440638869614</v>
-      </c>
-      <c r="C401" t="n">
-        <v>0.00000168472119691203</v>
-      </c>
-      <c r="D401" t="n">
-        <v>0.000000013701975295374</v>
-      </c>
-      <c r="E401" t="n">
-        <v>5.72282125336632</v>
-      </c>
-      <c r="F401" t="n">
-        <v>462.83665033446</v>
-      </c>
-      <c r="G401" t="s">
-        <v>73</v>
-      </c>
-      <c r="H401" t="n">
-        <v>0</v>
-      </c>
-      <c r="I401" t="n">
-        <v>0</v>
-      </c>
-      <c r="J401" t="s">
-        <v>21</v>
-      </c>
-      <c r="K401" t="n">
-        <v>1.386</v>
-      </c>
-      <c r="L401" t="s">
-        <v>15</v>
-      </c>
-      <c r="M401" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" s="1" t="n">
-        <v>44317</v>
-      </c>
-      <c r="B402" t="n">
-        <v>0.0087133881542496</v>
-      </c>
-      <c r="C402" t="n">
-        <v>0.00000303107361378077</v>
-      </c>
-      <c r="D402" t="n">
-        <v>0.0000000194229034816968</v>
-      </c>
-      <c r="E402" t="n">
-        <v>14.3669977974638</v>
-      </c>
-      <c r="F402" t="n">
-        <v>892.532289724704</v>
-      </c>
-      <c r="G402" t="s">
-        <v>73</v>
-      </c>
-      <c r="H402" t="n">
-        <v>1</v>
-      </c>
-      <c r="I402" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J402" t="s">
-        <v>14</v>
-      </c>
-      <c r="K402" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L402" t="s">
-        <v>15</v>
-      </c>
-      <c r="M402" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" s="1" t="n">
-        <v>44348</v>
-      </c>
-      <c r="B403" t="n">
-        <v>0.00473107113485681</v>
-      </c>
-      <c r="C403" t="n">
-        <v>0.00000149363976458398</v>
-      </c>
-      <c r="D403" t="n">
-        <v>0.00000000806360222789291</v>
-      </c>
-      <c r="E403" t="n">
-        <v>12.3102874617877</v>
-      </c>
-      <c r="F403" t="n">
-        <v>594.519448365611</v>
-      </c>
-      <c r="G403" t="s">
-        <v>73</v>
-      </c>
-      <c r="H403" t="n">
-        <v>0</v>
-      </c>
-      <c r="I403" t="n">
-        <v>0</v>
-      </c>
-      <c r="J403" t="s">
-        <v>21</v>
-      </c>
-      <c r="K403" t="n">
-        <v>1.473</v>
-      </c>
-      <c r="L403" t="s">
-        <v>15</v>
-      </c>
-      <c r="M403" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="1" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B404" t="n">
-        <v>0.00314209075977624</v>
-      </c>
-      <c r="C404" t="n">
-        <v>0.000000802351593335861</v>
-      </c>
-      <c r="D404" t="n">
-        <v>0.00000000133235512288788</v>
-      </c>
-      <c r="E404" t="n">
-        <v>13.0227239183357</v>
-      </c>
-      <c r="F404" t="n">
-        <v>989.446395224728</v>
-      </c>
-      <c r="G404" t="s">
-        <v>73</v>
-      </c>
-      <c r="H404" t="n">
-        <v>0</v>
-      </c>
-      <c r="I404" t="n">
-        <v>0</v>
-      </c>
-      <c r="J404" t="s">
-        <v>21</v>
-      </c>
-      <c r="K404" t="n">
-        <v>1.314</v>
-      </c>
-      <c r="L404" t="s">
-        <v>15</v>
-      </c>
-      <c r="M404" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="1" t="n">
-        <v>44409</v>
-      </c>
-      <c r="B405" t="n">
-        <v>0.00456136941824546</v>
-      </c>
-      <c r="C405" t="n">
-        <v>0.00000085588224042911</v>
-      </c>
-      <c r="D405" t="n">
-        <v>0.00000000221116255360453</v>
-      </c>
-      <c r="E405" t="n">
-        <v>19.340674079679</v>
-      </c>
-      <c r="F405" t="n">
-        <v>2638.79518997696</v>
-      </c>
-      <c r="G405" t="s">
-        <v>73</v>
-      </c>
-      <c r="H405" t="n">
-        <v>0</v>
-      </c>
-      <c r="I405" t="n">
-        <v>0</v>
-      </c>
-      <c r="J405" t="s">
-        <v>21</v>
-      </c>
-      <c r="K405" t="n">
-        <v>1.456</v>
-      </c>
-      <c r="L405" t="s">
-        <v>15</v>
-      </c>
-      <c r="M405" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="1" t="n">
-        <v>44440</v>
-      </c>
-      <c r="B406" t="n">
-        <v>0.0128475230854823</v>
-      </c>
-      <c r="C406" t="n">
-        <v>0.00000125138050786917</v>
-      </c>
-      <c r="D406" t="n">
-        <v>0.00000000405938851369447</v>
-      </c>
-      <c r="E406" t="n">
-        <v>75.4158354403962</v>
-      </c>
-      <c r="F406" t="n">
-        <v>2766.67013707449</v>
-      </c>
-      <c r="G406" t="s">
-        <v>73</v>
-      </c>
-      <c r="H406" t="n">
-        <v>0</v>
-      </c>
-      <c r="I406" t="n">
-        <v>0</v>
-      </c>
-      <c r="J406" t="s">
-        <v>21</v>
-      </c>
-      <c r="K406" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="L406" t="s">
-        <v>15</v>
-      </c>
-      <c r="M406" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B407" t="n">
-        <v>0.0156738398151598</v>
-      </c>
-      <c r="C407" t="n">
-        <v>0.00000173341075745611</v>
-      </c>
-      <c r="D407" t="n">
-        <v>0.00000000413417332367603</v>
-      </c>
-      <c r="E407" t="n">
-        <v>135.464303149179</v>
-      </c>
-      <c r="F407" t="n">
-        <v>14925.7335774714</v>
-      </c>
-      <c r="G407" t="s">
-        <v>73</v>
-      </c>
-      <c r="H407" t="n">
-        <v>0</v>
-      </c>
-      <c r="I407" t="n">
-        <v>0</v>
-      </c>
-      <c r="J407" t="s">
-        <v>21</v>
-      </c>
-      <c r="K407" t="n">
-        <v>2.567</v>
-      </c>
-      <c r="L407" t="s">
-        <v>15</v>
-      </c>
-      <c r="M407" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="1" t="n">
-        <v>44501</v>
-      </c>
-      <c r="B408" t="n">
-        <v>0.00469817558064714</v>
-      </c>
-      <c r="C408" t="n">
-        <v>0.000000282588358135708</v>
-      </c>
-      <c r="D408" t="n">
-        <v>0.0000000000953769422082247</v>
-      </c>
-      <c r="E408" t="n">
-        <v>44.6989425237277</v>
-      </c>
-      <c r="F408" t="n">
-        <v>10450.7967327013</v>
-      </c>
-      <c r="G408" t="s">
-        <v>73</v>
-      </c>
-      <c r="H408" t="n">
-        <v>0</v>
-      </c>
-      <c r="I408" t="n">
-        <v>0</v>
-      </c>
-      <c r="J408" t="s">
-        <v>21</v>
-      </c>
-      <c r="K408" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="L408" t="s">
-        <v>15</v>
-      </c>
-      <c r="M408" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="1" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B409" t="n">
-        <v>0.00315802566313303</v>
-      </c>
-      <c r="C409" t="n">
-        <v>0.000000125914638710897</v>
-      </c>
-      <c r="D409" t="n">
-        <v>0.000000000260166767084921</v>
-      </c>
-      <c r="E409" t="n">
-        <v>52.2894504845504</v>
-      </c>
-      <c r="F409" t="n">
-        <v>6439.6432167397</v>
-      </c>
-      <c r="G409" t="s">
-        <v>73</v>
-      </c>
-      <c r="H409" t="n">
-        <v>0</v>
-      </c>
-      <c r="I409" t="n">
-        <v>0</v>
-      </c>
-      <c r="J409" t="s">
-        <v>21</v>
-      </c>
-      <c r="K409" t="n">
-        <v>1.316</v>
-      </c>
-      <c r="L409" t="s">
-        <v>15</v>
-      </c>
-      <c r="M409" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="1" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B410" t="n">
-        <v>0.00207895027356704</v>
-      </c>
-      <c r="C410" t="n">
-        <v>0.0000000575650659826958</v>
-      </c>
-      <c r="D410" t="n">
-        <v>0.0000000000440175157878839</v>
-      </c>
-      <c r="E410" t="n">
-        <v>47.1170660125407</v>
-      </c>
-      <c r="F410" t="n">
-        <v>8452.11498746779</v>
-      </c>
-      <c r="G410" t="s">
-        <v>73</v>
-      </c>
-      <c r="H410" t="n">
-        <v>0</v>
-      </c>
-      <c r="I410" t="n">
-        <v>0</v>
-      </c>
-      <c r="J410" t="s">
-        <v>21</v>
-      </c>
-      <c r="K410" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="L410" t="s">
-        <v>15</v>
-      </c>
-      <c r="M410" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B411" t="n">
-        <v>0.00261836055153602</v>
-      </c>
-      <c r="C411" t="n">
-        <v>0.000000103005358115792</v>
-      </c>
-      <c r="D411" t="n">
-        <v>0.0000000000602631271682811</v>
-      </c>
-      <c r="E411" t="n">
-        <v>50.9579326967514</v>
-      </c>
-      <c r="F411" t="n">
-        <v>14141.4412340919</v>
-      </c>
-      <c r="G411" t="s">
-        <v>73</v>
-      </c>
-      <c r="H411" t="n">
-        <v>0</v>
-      </c>
-      <c r="I411" t="n">
-        <v>0</v>
-      </c>
-      <c r="J411" t="s">
-        <v>21</v>
-      </c>
-      <c r="K411" t="n">
-        <v>1.262</v>
-      </c>
-      <c r="L411" t="s">
-        <v>15</v>
-      </c>
-      <c r="M411" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="B412" t="n">
-        <v>0.00566028345179814</v>
-      </c>
-      <c r="C412" t="n">
-        <v>0.00000013304380401547</v>
-      </c>
-      <c r="D412" t="n">
-        <v>0.0000000000570980000477877</v>
-      </c>
-      <c r="E412" t="n">
-        <v>177.194478067265</v>
-      </c>
-      <c r="F412" t="n">
-        <v>52990.3425257093</v>
-      </c>
-      <c r="G412" t="s">
-        <v>73</v>
-      </c>
-      <c r="H412" t="n">
-        <v>0</v>
-      </c>
-      <c r="I412" t="n">
-        <v>0</v>
-      </c>
-      <c r="J412" t="s">
-        <v>21</v>
-      </c>
-      <c r="K412" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="L412" t="s">
-        <v>15</v>
-      </c>
-      <c r="M412" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B413" t="n">
-        <v>0.00144530621919117</v>
-      </c>
-      <c r="C413" t="n">
-        <v>0.0000000100275512259777</v>
-      </c>
-      <c r="D413" t="n">
-        <v>0.00000000000830367781959773</v>
-      </c>
-      <c r="E413" t="n">
-        <v>91.6156873187214</v>
-      </c>
-      <c r="F413" t="n">
-        <v>60489.1516510707</v>
-      </c>
-      <c r="G413" t="s">
-        <v>73</v>
-      </c>
-      <c r="H413" t="n">
-        <v>0</v>
-      </c>
-      <c r="I413" t="n">
-        <v>0</v>
-      </c>
-      <c r="J413" t="s">
-        <v>21</v>
-      </c>
-      <c r="K413" t="n">
-        <v>1.145</v>
-      </c>
-      <c r="L413" t="s">
-        <v>15</v>
-      </c>
-      <c r="M413" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="B414" t="n">
-        <v>0.00353892574646135</v>
-      </c>
-      <c r="C414" t="n">
-        <v>0.0000000303605237153436</v>
-      </c>
-      <c r="D414" t="n">
-        <v>0.0000000000190360634660442</v>
-      </c>
-      <c r="E414" t="n">
-        <v>139.756752175198</v>
-      </c>
-      <c r="F414" t="n">
-        <v>152134.74616207</v>
-      </c>
-      <c r="G414" t="s">
-        <v>73</v>
-      </c>
-      <c r="H414" t="n">
-        <v>0</v>
-      </c>
-      <c r="I414" t="n">
-        <v>0</v>
-      </c>
-      <c r="J414" t="s">
-        <v>21</v>
-      </c>
-      <c r="K414" t="n">
-        <v>1.354</v>
-      </c>
-      <c r="L414" t="s">
-        <v>15</v>
-      </c>
-      <c r="M414" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B415" t="n">
-        <v>0.00196889055691249</v>
-      </c>
-      <c r="C415" t="n">
-        <v>0.0000000111691433206</v>
-      </c>
-      <c r="D415" t="n">
-        <v>0.00000000000261882623382056</v>
-      </c>
-      <c r="E415" t="n">
-        <v>139.068600934029</v>
-      </c>
-      <c r="F415" t="n">
-        <v>205088.314254645</v>
-      </c>
-      <c r="G415" t="s">
-        <v>73</v>
-      </c>
-      <c r="H415" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>0</v>
-      </c>
-      <c r="J415" t="s">
-        <v>21</v>
-      </c>
-      <c r="K415" t="n">
-        <v>1.197</v>
-      </c>
-      <c r="L415" t="s">
-        <v>15</v>
-      </c>
-      <c r="M415" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" s="1" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B416" t="n">
-        <v>0.00115201466094649</v>
-      </c>
-      <c r="C416" t="n">
-        <v>0.00000000395103146899154</v>
-      </c>
-      <c r="D416" t="n">
-        <v>0.0000000000014335845481669</v>
-      </c>
-      <c r="E416" t="n">
-        <v>157.946128167366</v>
-      </c>
-      <c r="F416" t="n">
-        <v>110850.49337011</v>
-      </c>
-      <c r="G416" t="s">
-        <v>73</v>
-      </c>
-      <c r="H416" t="n">
-        <v>1</v>
-      </c>
-      <c r="I416" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J416" t="s">
-        <v>14</v>
-      </c>
-      <c r="K416" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L416" t="s">
-        <v>15</v>
-      </c>
-      <c r="M416" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="B417" t="n">
-        <v>0.00131904178337669</v>
-      </c>
-      <c r="C417" t="n">
-        <v>0.00000000216529419393388</v>
-      </c>
-      <c r="D417" t="n">
-        <v>0.00000000000113296900077354</v>
-      </c>
-      <c r="E417" t="n">
-        <v>145.043411007742</v>
-      </c>
-      <c r="F417" t="n">
-        <v>107195.957772336</v>
-      </c>
-      <c r="G417" t="s">
-        <v>73</v>
-      </c>
-      <c r="H417" t="n">
-        <v>1</v>
-      </c>
-      <c r="I417" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J417" t="s">
-        <v>14</v>
-      </c>
-      <c r="K417" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L417" t="s">
-        <v>15</v>
-      </c>
-      <c r="M417" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" s="1" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B418" t="n">
-        <v>0.00441827610976025</v>
-      </c>
-      <c r="C418" t="n">
-        <v>0.00000000938468758710215</v>
-      </c>
-      <c r="D418" t="n">
-        <v>0.000000000000693871690877543</v>
-      </c>
-      <c r="E418" t="n">
-        <v>1185.36815069609</v>
-      </c>
-      <c r="F418" t="n">
-        <v>966657.24460087</v>
-      </c>
-      <c r="G418" t="s">
-        <v>73</v>
-      </c>
-      <c r="H418" t="n">
-        <v>0</v>
-      </c>
-      <c r="I418" t="n">
-        <v>0</v>
-      </c>
-      <c r="J418" t="s">
-        <v>21</v>
-      </c>
-      <c r="K418" t="n">
-        <v>1.442</v>
-      </c>
-      <c r="L418" t="s">
-        <v>15</v>
-      </c>
-      <c r="M418" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B419" t="n">
-        <v>0.00655861254207205</v>
-      </c>
-      <c r="C419" t="n">
-        <v>0.0000000110507996836</v>
-      </c>
-      <c r="D419" t="n">
-        <v>0.000000000000479670957473394</v>
-      </c>
-      <c r="E419" t="n">
-        <v>3887.75144387638</v>
-      </c>
-      <c r="F419" t="n">
-        <v>8020211.66798369</v>
-      </c>
-      <c r="G419" t="s">
-        <v>73</v>
-      </c>
-      <c r="H419" t="n">
-        <v>1</v>
-      </c>
-      <c r="I419" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J419" t="s">
-        <v>14</v>
-      </c>
-      <c r="K419" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="L419" t="s">
-        <v>15</v>
-      </c>
-      <c r="M419" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B420" t="n">
-        <v>0.00175320256489333</v>
-      </c>
-      <c r="C420" t="n">
-        <v>0.00000000194481930147967</v>
-      </c>
-      <c r="D420" t="n">
-        <v>0.0000000000000519083096339178</v>
-      </c>
-      <c r="E420" t="n">
-        <v>858.631802955096</v>
-      </c>
-      <c r="F420" t="n">
-        <v>1573664.8171057</v>
-      </c>
-      <c r="G420" t="s">
-        <v>73</v>
-      </c>
-      <c r="H420" t="n">
-        <v>0</v>
-      </c>
-      <c r="I420" t="n">
-        <v>0</v>
-      </c>
-      <c r="J420" t="s">
-        <v>21</v>
-      </c>
-      <c r="K420" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="L420" t="s">
-        <v>15</v>
-      </c>
-      <c r="M420" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B421" t="n">
-        <v>0.00124359012850774</v>
-      </c>
-      <c r="C421" t="n">
-        <v>0.00000000104719418523707</v>
-      </c>
-      <c r="D421" t="n">
-        <v>0.0000000000000197863265749655</v>
-      </c>
-      <c r="E421" t="n">
-        <v>1023.01195581129</v>
-      </c>
-      <c r="F421" t="n">
-        <v>805218.627877096</v>
-      </c>
-      <c r="G421" t="s">
-        <v>73</v>
-      </c>
-      <c r="H421" t="n">
-        <v>2</v>
-      </c>
-      <c r="I421" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J421" t="s">
-        <v>14</v>
-      </c>
-      <c r="K421" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="L421" t="s">
-        <v>15</v>
-      </c>
-      <c r="M421" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B422" t="n">
-        <v>0.000747052325084002</v>
-      </c>
-      <c r="C422" t="n">
-        <v>0.000000000261046107578163</v>
-      </c>
-      <c r="D422" t="n">
-        <v>0.0000000000000178588469444189</v>
-      </c>
-      <c r="E422" t="n">
-        <v>846.784528332662</v>
-      </c>
-      <c r="F422" t="n">
-        <v>2278991.22141257</v>
-      </c>
-      <c r="G422" t="s">
-        <v>73</v>
-      </c>
-      <c r="H422" t="n">
-        <v>0</v>
-      </c>
-      <c r="I422" t="n">
-        <v>0</v>
-      </c>
-      <c r="J422" t="s">
-        <v>21</v>
-      </c>
-      <c r="K422" t="n">
-        <v>1.075</v>
-      </c>
-      <c r="L422" t="s">
-        <v>15</v>
-      </c>
-      <c r="M422" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" s="1" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B423" t="n">
-        <v>0.00116537362752276</v>
-      </c>
-      <c r="C423" t="n">
-        <v>0.000000000418669773708802</v>
-      </c>
-      <c r="D423" t="n">
-        <v>0.0000000000000120657077742026</v>
-      </c>
-      <c r="E423" t="n">
-        <v>2205.01920727789</v>
-      </c>
-      <c r="F423" t="n">
-        <v>4549158.28208498</v>
-      </c>
-      <c r="G423" t="s">
-        <v>73</v>
-      </c>
-      <c r="H423" t="n">
-        <v>0</v>
-      </c>
-      <c r="I423" t="n">
-        <v>0</v>
-      </c>
-      <c r="J423" t="s">
-        <v>21</v>
-      </c>
-      <c r="K423" t="n">
-        <v>1.117</v>
-      </c>
-      <c r="L423" t="s">
-        <v>15</v>
-      </c>
-      <c r="M423" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" s="1" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B424" t="n">
-        <v>0.00260645252712793</v>
-      </c>
-      <c r="C424" t="n">
-        <v>0.000000000568954881186178</v>
-      </c>
-      <c r="D424" t="n">
-        <v>0.0000000000000055324510675496</v>
-      </c>
-      <c r="E424" t="n">
-        <v>4007.51324028039</v>
-      </c>
-      <c r="F424" t="n">
-        <v>11922130.5283762</v>
-      </c>
-      <c r="G424" t="s">
-        <v>73</v>
-      </c>
-      <c r="H424" t="n">
-        <v>1</v>
-      </c>
-      <c r="I424" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J424" t="s">
-        <v>14</v>
-      </c>
-      <c r="K424" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L424" t="s">
-        <v>15</v>
-      </c>
-      <c r="M424" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="1" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B425" t="n">
-        <v>0.000642580982909592</v>
-      </c>
-      <c r="C425" t="n">
-        <v>0.0000000000652506022710883</v>
-      </c>
-      <c r="D425" t="n">
-        <v>0.000000000000000623765007581373</v>
-      </c>
-      <c r="E425" t="n">
-        <v>3454.66725106221</v>
-      </c>
-      <c r="F425" t="n">
-        <v>6832676.84895945</v>
-      </c>
-      <c r="G425" t="s">
-        <v>73</v>
-      </c>
-      <c r="H425" t="n">
-        <v>0</v>
-      </c>
-      <c r="I425" t="n">
-        <v>0</v>
-      </c>
-      <c r="J425" t="s">
-        <v>21</v>
-      </c>
-      <c r="K425" t="n">
-        <v>1.064</v>
-      </c>
-      <c r="L425" t="s">
-        <v>15</v>
-      </c>
-      <c r="M425" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B426" t="n">
-        <v>0.00149242825782812</v>
-      </c>
-      <c r="C426" t="n">
-        <v>0.000000000163700810177067</v>
-      </c>
-      <c r="D426" t="n">
-        <v>0.000000000000000631326531020606</v>
-      </c>
-      <c r="E426" t="n">
-        <v>9034.52661732549</v>
-      </c>
-      <c r="F426" t="n">
-        <v>38781347.8707074</v>
-      </c>
-      <c r="G426" t="s">
-        <v>73</v>
-      </c>
-      <c r="H426" t="n">
-        <v>0</v>
-      </c>
-      <c r="I426" t="n">
-        <v>0</v>
-      </c>
-      <c r="J426" t="s">
-        <v>21</v>
-      </c>
-      <c r="K426" t="n">
-        <v>1.149</v>
-      </c>
-      <c r="L426" t="s">
-        <v>15</v>
-      </c>
-      <c r="M426" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B427" t="n">
-        <v>0.00081726119688067</v>
-      </c>
-      <c r="C427" t="n">
-        <v>0.0000000000405567832159461</v>
-      </c>
-      <c r="D427" t="n">
-        <v>0.000000000000000295749533241578</v>
-      </c>
-      <c r="E427" t="n">
-        <v>4418.68084055192</v>
-      </c>
-      <c r="F427" t="n">
-        <v>117391773.092818</v>
-      </c>
-      <c r="G427" t="s">
-        <v>73</v>
-      </c>
-      <c r="H427" t="n">
-        <v>1</v>
-      </c>
-      <c r="I427" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J427" t="s">
-        <v>14</v>
-      </c>
-      <c r="K427" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L427" t="s">
-        <v>15</v>
-      </c>
-      <c r="M427" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" s="1" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B428" t="n">
-        <v>0.000523815726438287</v>
-      </c>
-      <c r="C428" t="n">
-        <v>0.0000000000257795018987544</v>
-      </c>
-      <c r="D428" t="n">
-        <v>0.0000000000000000512725889607116</v>
-      </c>
-      <c r="E428" t="n">
-        <v>5734.82389116552</v>
-      </c>
-      <c r="F428" t="n">
-        <v>42939687.7459297</v>
-      </c>
-      <c r="G428" t="s">
-        <v>73</v>
-      </c>
-      <c r="H428" t="n">
-        <v>2</v>
-      </c>
-      <c r="I428" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J428" t="s">
-        <v>14</v>
-      </c>
-      <c r="K428" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L428" t="s">
-        <v>15</v>
-      </c>
-      <c r="M428" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B429" t="n">
-        <v>0.000723241012785071</v>
-      </c>
-      <c r="C429" t="n">
-        <v>0.0000000000144725694840193</v>
-      </c>
-      <c r="D429" t="n">
-        <v>0.0000000000000000321984108798186</v>
-      </c>
-      <c r="E429" t="n">
-        <v>4865.52256083138</v>
-      </c>
-      <c r="F429" t="n">
-        <v>56521251.7082073</v>
-      </c>
-      <c r="G429" t="s">
-        <v>73</v>
-      </c>
-      <c r="H429" t="n">
-        <v>0</v>
-      </c>
-      <c r="I429" t="n">
-        <v>0</v>
-      </c>
-      <c r="J429" t="s">
-        <v>21</v>
-      </c>
-      <c r="K429" t="n">
-        <v>1.072</v>
-      </c>
-      <c r="L429" t="s">
-        <v>15</v>
-      </c>
-      <c r="M429" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B430" t="n">
-        <v>0.00225366948426119</v>
-      </c>
-      <c r="C430" t="n">
-        <v>0.0000000000694466565434294</v>
-      </c>
-      <c r="D430" t="n">
-        <v>0.000000000000000149984610604803</v>
-      </c>
-      <c r="E430" t="n">
-        <v>32331.3584221533</v>
-      </c>
-      <c r="F430" t="n">
-        <v>392865425.402835</v>
-      </c>
-      <c r="G430" t="s">
-        <v>73</v>
-      </c>
-      <c r="H430" t="n">
-        <v>1</v>
-      </c>
-      <c r="I430" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J430" t="s">
-        <v>14</v>
-      </c>
-      <c r="K430" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L430" t="s">
-        <v>15</v>
-      </c>
-      <c r="M430" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" s="1" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B431" t="n">
-        <v>0.0027668498665217</v>
-      </c>
-      <c r="C431" t="n">
-        <v>0.000000000082617491592387</v>
-      </c>
-      <c r="D431" t="n">
-        <v>0.00000000000000050563641851999</v>
-      </c>
-      <c r="E431" t="n">
-        <v>38362.6473138185</v>
-      </c>
-      <c r="F431" t="n">
-        <v>3049897668.7446</v>
-      </c>
-      <c r="G431" t="s">
-        <v>73</v>
-      </c>
-      <c r="H431" t="n">
-        <v>1</v>
-      </c>
-      <c r="I431" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J431" t="s">
-        <v>14</v>
-      </c>
-      <c r="K431" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="L431" t="s">
-        <v>15</v>
-      </c>
-      <c r="M431" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="1" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B432" t="n">
-        <v>0.000818635492374786</v>
-      </c>
-      <c r="C432" t="n">
-        <v>0.0000000000121813949410073</v>
-      </c>
-      <c r="D432" t="n">
-        <v>0.000000000000000018503780896728</v>
-      </c>
-      <c r="E432" t="n">
-        <v>16516.1884899858</v>
-      </c>
-      <c r="F432" t="n">
-        <v>1374116894.6605</v>
-      </c>
-      <c r="G432" t="s">
-        <v>73</v>
-      </c>
-      <c r="H432" t="n">
-        <v>0</v>
-      </c>
-      <c r="I432" t="n">
-        <v>0</v>
-      </c>
-      <c r="J432" t="s">
-        <v>21</v>
-      </c>
-      <c r="K432" t="n">
-        <v>1.082</v>
-      </c>
-      <c r="L432" t="s">
-        <v>15</v>
-      </c>
-      <c r="M432" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B433" t="n">
-        <v>0.000554436122259873</v>
-      </c>
-      <c r="C433" t="n">
-        <v>0.0000000000045792422361419</v>
-      </c>
-      <c r="D433" t="n">
-        <v>0.00000000000000000190398248140046</v>
-      </c>
-      <c r="E433" t="n">
-        <v>13425.857592354</v>
-      </c>
-      <c r="F433" t="n">
-        <v>1130870599.98038</v>
-      </c>
-      <c r="G433" t="s">
-        <v>73</v>
-      </c>
-      <c r="H433" t="n">
-        <v>0</v>
-      </c>
-      <c r="I433" t="n">
-        <v>0</v>
-      </c>
-      <c r="J433" t="s">
-        <v>21</v>
-      </c>
-      <c r="K433" t="n">
-        <v>1.055</v>
-      </c>
-      <c r="L433" t="s">
-        <v>15</v>
-      </c>
-      <c r="M433" t="s">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
